--- a/data/history/CyberJobs_21062026.xlsx
+++ b/data/history/CyberJobs_21062026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyber Jobs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Cyber Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <name val="Segoe UI"/>
@@ -83,19 +80,13 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
     </border>
     <border>
       <left style="thin">
@@ -131,30 +122,30 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -522,15 +513,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="93" customWidth="1" min="5" max="5"/>
-    <col width="455" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="63" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="381" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -544,7 +535,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report Generated: June 21, 2026 - 12:44 AM | Total Jobs: 23</t>
+          <t>Report Generated: June 21, 2026 - 02:01 AM | Total Jobs: 10</t>
         </is>
       </c>
     </row>
@@ -592,32 +583,32 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Robinhood</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer, Security Analytics Infrastructure</t>
+          <t>Security Engineer, Detection &amp; Response</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>US - Remote</t>
+          <t>Menlo Park, CA</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>5 years | Claude: Legitimate security engineering role (SIEM, threat detection, security analytics infrastructure) at US remote location targeting software engineers with security expertise.</t>
+          <t>4 years | Claude: This is a USA-based (Menlo Park, CA) Security Operations/Detection &amp; Response role that aligns with legitimate cybersecurity functions (SOC, Incident Response, threat detection) and does not specify experience requirements beyond what would typically target mid-level professionals.</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7826761</t>
+          <t>https://boards.greenhouse.io/robinhood/jobs/7697725?t=gh_src=&amp;gh_jid=7697725</t>
         </is>
       </c>
     </row>
@@ -627,32 +618,32 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Chainguard</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Compliance Exam Lead</t>
+          <t>Senior Product Security Engineer</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>Remote US</t>
+          <t>United States - Remote</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>5 years | Claude: This is a Remote-US compliance role targeting an experienced professional to manage regulatory exam engagements, which falls squarely within GRC/Compliance cybersecurity functions.</t>
+          <t>5 years | Claude: Senior Product Security Engineer is a legitimate DevSecOps/Product Security role requiring 5-7 years experience, located in US Remote, meeting all three criteria.</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/7713708003</t>
+          <t>https://job-boards.greenhouse.io/chainguard/jobs/4688970006</t>
         </is>
       </c>
     </row>
@@ -662,32 +653,32 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Chainguard</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Compliance Operations Analyst</t>
+          <t>Senior Security Engineer (AI Platform)</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>United States - Remote</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>3 years | Claude: This is a USA-based (Denver, CO) cybersecurity compliance role targeting mid-level experience, falling squarely within the 1-6 year range for a Compliance Operations Analyst position.</t>
+          <t>5 years | Claude: Senior Security Engineer role in cybersecurity (AI platform security/governance) located in United States remote, though "Senior" title suggests 7+ years experience which conflicts with the 1-6 year requirement—this is a borderline rejection on Criterion 3.</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>https://www.klaviyo.com/careers/jobs/7723889003?gh_jid=7723889003</t>
+          <t>https://job-boards.greenhouse.io/chainguard/jobs/4687742006</t>
         </is>
       </c>
     </row>
@@ -697,32 +688,32 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Chime</t>
+          <t>1Password</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Senior Offensive Security Engineer</t>
+          <t>Senior Developer, Product Security</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, USA</t>
+          <t>Remote (United States | Canada)</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>4 years | Claude: This is a Senior Offensive Security Engineer role (legitimate cybersecurity position in penetration testing/red team) located in San Francisco, USA, but it targets senior-level experience (7+ years implied by "Senior" title and leadership requirements), which exceeds the 1-6 year criteria.</t>
+          <t>5 years, 3 years | Claude: All three criteria satisfied: US-remote location, legitimate Product Security/AppSec role, and Senior Developer level implies 5-8 years experience targeting the mid-to-senior range within acceptable bounds.</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/chime/jobs/8121830002?gh_jid=8121830002</t>
+          <t>https://jobs.ashbyhq.com/1password/79442471-c467-479a-beb0-38593cab0edc</t>
         </is>
       </c>
     </row>
@@ -732,32 +723,32 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Abnormal Security</t>
+          <t>1Password</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Security Analyst</t>
+          <t>Senior Security Engineer, GRC Automation</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Remote - USA</t>
+          <t>Remote (United States | Canada)</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Not specified (Assumed 1-6 yrs) | Claude: This is a remote-USA Security Analyst role at a legitimate cybersecurity company (email security/threat intelligence) requiring less than 1 year of experience, meeting all three criteria.</t>
+          <t>5 years | Claude: Senior Security Engineer is a legitimate GRC/compliance cybersecurity role, located in Remote-US, targeting mid-to-senior level experience (typically 5-8 years), which falls within the 1-6 year target range as a mid-level to senior boundary role.</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>https://abnormal.ai/careers/jobs/7611937003?gh_jid=7611937003</t>
+          <t>https://jobs.ashbyhq.com/1password/739b8cc9-6c96-4afb-825e-1bf5aa5e1f00</t>
         </is>
       </c>
     </row>
@@ -767,32 +758,32 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Verkada</t>
+          <t>Horizon3.ai</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Lead Product Manager, Security Trailers</t>
+          <t>Manager, Security Engineering, Cloud &amp; AppSec</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>San Mateo, CA United States</t>
+          <t>US, Remote</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>5 years | Claude: All three criteria met: USA location (San Mateo, CA), legitimate cybersecurity role (physical security/video surveillance product management for threat detection platform), and lead/mid-level PM position typically targeting experienced professionals in the 1-6+ year range.</t>
+          <t>5 years, 5 years | Claude: This is a US-remote management role in cloud security and application security engineering, requiring leadership experience (typically 5-8 years), which falls within the 1-6 year target range for mid-to-senior level candidates.</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/verkada/jobs/5062987007</t>
+          <t>https://jobs.ashbyhq.com/horizon3ai/f1ec575d-6be7-448f-bcca-1966a42128b4</t>
         </is>
       </c>
     </row>
@@ -802,32 +793,32 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>Dragos</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Senior Security Engineer, Application Security</t>
+          <t>Associate Principal OT Penetration Tester</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Bellevue, WA; Menlo Park, CA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>5 years | Claude: Senior AppSec role at US locations (Bellevue, WA; Menlo Park, CA) targeting experienced mid-to-senior level engineers (typically 5-8 years), which overlaps the 1-6 year range at the upper end and is a legitimate cybersecurity position.</t>
+          <t>5 years | Claude: This is a USA-based penetration testing role (legitimate cybersecurity discipline) targeting senior mid-level to principal experience, which exceeds the 1-6 year requirement and should be rejected on experience level grounds.</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/robinhood/jobs/7918258?t=gh_src=&amp;gh_jid=7918258</t>
+          <t>https://job-boards.greenhouse.io/dragos/jobs/5160432008</t>
         </is>
       </c>
     </row>
@@ -837,32 +828,32 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>LaunchDarkly</t>
+          <t>Horizon3.ai</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>Security Analyst - Governance, Risk, and Compliance</t>
+          <t>WebApp Offensive Security Software Engineer</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>US, Remote</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>Not specified (Assumed 1-6 yrs) | Claude: This is a legitimate GRC security role located in Remote-US; however, "Security Analyst III" typically indicates 5+ years of experience, which falls within the acceptable 1-6 year range, though it skews toward the mid-to-senior end.</t>
+          <t>Not specified (Assumed 1-6 yrs) | Claude: Offensive Security Software Engineer is a legitimate cybersecurity role (penetration testing/AppSec) located in the US (remote), and the job description does not specify experience requirements beyond "extensive web application penetration testing experience," which typically indicates mid-level positioning consistent with 1-6 years.</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/launchdarkly/jobs/7753776003</t>
+          <t>https://jobs.ashbyhq.com/horizon3ai/3a664c46-88f2-4367-8aa1-4413d29acd19</t>
         </is>
       </c>
     </row>
@@ -872,32 +863,32 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Senior Compliance Tech Analyst, Platform (Compliance Automation)</t>
+          <t>Senior Software Engineer, Cryptography &amp; Secrets Management</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Remote - USA</t>
+          <t>El Dorado Hills, California, United States</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>3-5 years, 5 years | Claude: This is a USA remote cybersecurity/compliance role (GRC/Compliance domain) targeting mid-level experience (Senior Analyst typically requires 3-6 years).</t>
+          <t>5 years | Claude: Role is US-based (remote with CA office option), legitimate senior cryptography/secrets management cybersecurity position, but experience level is ambiguous—"Senior" typically implies 7+ years, which would exceed the 1-6 year target range.</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>https://www.coinbase.com/careers/positions/7947120?gh_jid=7947120</t>
+          <t>https://job-boards.greenhouse.io/keepersecurity/jobs/4091113009</t>
         </is>
       </c>
     </row>
@@ -907,487 +898,32 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Brex</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Senior Security Operations Engineer</t>
+          <t>Software Engineer, Infrastructure Security</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>Seattle, Washington, United States</t>
+          <t>Remote - US</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>5 years | Claude: This is a legitimate cybersecurity role (Security Operations Engineer/SOC) in Seattle, Washington (US location), but the "Senior" title and typical requirements for such positions suggest 7+ years of experience, which exceeds the 1-6 year target range.</t>
+          <t>Not specified (Assumed 1-6 yrs) | Claude: Role is located in Remote-US, is a legitimate cybersecurity/infrastructure security engineering position (authentication, access control, key management), and targets mid-level engineers within the 1-6 year experience range.</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>https://www.brex.com/careers/8339283002?gh_jid=8339283002</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Figma</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>Governance Risk and Compliance</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>San Francisco, CA • New York, NY • United States</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>4 years | Claude: This is a legitimate GRC (Governance, Risk, and Compliance) cybersecurity role located in the US (San Francisco, CA and New York, NY) that appears to target mid-level professionals based on the described responsibilities.</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/figma/jobs/6015630004?gh_jid=6015630004</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Benchling</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>Enterprise Security Engineer</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>5 years | Claude: Enterprise Security Engineer is a legitimate mid-level cybersecurity role (IAM/Zero Trust/SecOps focus) located in San Francisco, CA, targeting engineers with practical security experience.</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/benchling/b1828d61-38fe-4a28-9631-add78cacc4dd</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Drata</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>Senior Compliance Advisor</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>Remote - US</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>4-6 years, 6 years | Claude: Senior Compliance Advisor is a legitimate GRC/Compliance cybersecurity role, located Remote-US, targeting mid-to-senior level experience (1-6+ years acceptable for mid-level candidates).</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/drata/002e9df1-ac62-497a-8f0d-1ea475dd4340</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Tanium</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>IT Security Engineer</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>Addison, TX (Hybrid); Bellevue, WA (Hybrid); Durham, NC (Hybrid); Emeryville, CA (Hybrid)</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t>5 years | Claude: USA location (4 hybrid US offices), legitimate cybersecurity role (SIEM/SOAR/endpoint security/incident response), and mid-level experience requirement (1-6 years).</t>
-        </is>
-      </c>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/tanium/jobs/7874958</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>Paxos</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>Engineering Manager, Product Security</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>Remote - United States</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>8 years, 3 years | Claude: This is a legitimate cybersecurity engineering management role (Cloud Security, AppSec, SecOps) located in remote-US at a fintech company, targeting experienced security engineers with hands-on expertise rather than entry-level or 10+ year principal roles.</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/paxos/3a037300-1a7c-49eb-9e31-b5374f4a76c5</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Tailscale</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>Security Software Engineer</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>Remote (United States)</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>Not specified (Assumed 1-6 yrs) | Claude: Remote US location, legitimate AppSec/Security Engineering role with 50% development focus, and experience level appears mid-career without explicit seniority requirements.</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/tailscale/jobs/4648916005</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>Bugcrowd</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>Product Security Engineering Manager</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>Remote - US</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>7 years, 2 years | Claude: Remote-US location, legitimate Product Security Engineering Manager role (AppSec/Platform Security), but this is a manager-level position that typically requires 7+ years experience, making it outside the 1-6 year target range.</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/bugcrowd/jobs/7793504?gh_jid=7793504</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>Datadog</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>Senior Cloud Security Engineer - K8s</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>New York, New York, USA</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>Assumed mid-level senior | Claude: This is a legitimate cloud security engineering role (Cloud Security, K8s, infrastructure security) located in the USA (New York), but it targets Senior-level experience which typically requires 5-7+ years, placing it at the upper boundary or slightly beyond the 1-6 year range; however, the "Senior" title with cloud security specialization could reasonably attract candidates with 5-6 years of targeted experience.</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="inlineStr">
-        <is>
-          <t>https://careers.datadoghq.com/detail/7815616/?gh_jid=7815616</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>Menlo Security</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>Security Engineer</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>US - Distributed</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>Not specified (Assumed 1-6 yrs) | Claude: This is a legitimate cloud security/SecOps role targeting mid-level engineers in a US-distributed position, focusing on security automation, CSPM/CNAPP/CWPP tools, and CI/CD pipeline security.</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/menlosecurity/4a504b99-e5d6-445c-8a16-5fb4755421bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>2026-01-27</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Keeper Security</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer, Cybersecurity / Threat Detection</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>Remote, US</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>5 years | Claude: USA-based remote role in legitimate cybersecurity (threat detection/ML for PAM platform), and while "Senior" suggests experience, the role targets ML engineers in a specialized security domain typically filled by mid-to-senior talent within the 1-6 year range rather than C-suite/principal engineers requiring 10+ years.</t>
-        </is>
-      </c>
-      <c r="G24" s="10" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/keepersecurity/jobs/4105214009</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>Ramp</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>Security Engineer, Product</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>New York, NY (HQ)</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>5 years, 2 years | Claude: USA location (New York, NY), legitimate cybersecurity role (AppSec/Product Security Engineer), and mid-level experience target (1-6 years based on "Security Engineer" title and responsibilities).</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/ramp/7c26780b-7923-42d5-8111-9825ff996966</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>2025-12-23</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>1Password</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>Senior Security Engineer, Incident Response</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>Remote (United States | Canada)</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>5 years, 3 years | Claude: USA-based remote position, legitimate incident response/security engineering role, and senior level typically requires 5-7 years experience which falls within acceptable range.</t>
-        </is>
-      </c>
-      <c r="G26" s="10" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/1password/2951e57f-d0c1-4cdc-b0b7-ed62075aaf9a</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>Security Engineer, Infrastructure Security</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>Remote - US</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>Not specified (Assumed 1-6 yrs) | Claude: This is a legitimate Infrastructure Security/Security Engineering role located in Remote-US, and while experience level isn't explicitly stated, the role description targets mid-level engineers with "deep understanding of security principles" rather than entry-level or 10+ year staff positions.</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/openai/f51f750f-a737-4441-8f96-30133a2a8049</t>
+          <t>https://jobs.ashbyhq.com/openai/98ad9beb-4f91-496c-bd16-ac0b2a8d5bb2</t>
         </is>
       </c>
     </row>
@@ -1403,19 +939,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
